--- a/orders.xlsx
+++ b/orders.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9961" uniqueCount="2469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9993" uniqueCount="2477">
   <si>
     <t>Ngày tạo đơn</t>
   </si>
@@ -7418,6 +7418,30 @@
   </si>
   <si>
     <t>17097627468146</t>
+  </si>
+  <si>
+    <t>Yusuf Rahman</t>
+  </si>
+  <si>
+    <t>17156666786162</t>
+  </si>
+  <si>
+    <t>Mrs Shyfullz</t>
+  </si>
+  <si>
+    <t>17156588470642</t>
+  </si>
+  <si>
+    <t>Aini Omar</t>
+  </si>
+  <si>
+    <t>17156575527282</t>
+  </si>
+  <si>
+    <t>amellia quah</t>
+  </si>
+  <si>
+    <t>17156530209138</t>
   </si>
 </sst>
 </file>
@@ -7811,7 +7835,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J1274"/>
+  <dimension ref="A1:J1278"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="10" width="25" customWidth="1"/>
@@ -48585,6 +48609,134 @@
         <v>34</v>
       </c>
     </row>
+    <row r="1275" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1275" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1275" s="3">
+        <v>2</v>
+      </c>
+      <c r="C1275" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1275" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1275" s="3" t="s">
+        <v>2469</v>
+      </c>
+      <c r="F1275" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1275" s="3" t="s">
+        <v>2470</v>
+      </c>
+      <c r="H1275" s="3">
+        <v>69</v>
+      </c>
+      <c r="I1275" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1275" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1276" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1276" s="3">
+        <v>1</v>
+      </c>
+      <c r="C1276" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1276" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1276" s="3" t="s">
+        <v>2471</v>
+      </c>
+      <c r="F1276" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1276" s="3" t="s">
+        <v>2472</v>
+      </c>
+      <c r="H1276" s="3">
+        <v>183</v>
+      </c>
+      <c r="I1276" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1276" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1277" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1277" s="3">
+        <v>1</v>
+      </c>
+      <c r="C1277" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1277" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E1277" s="3" t="s">
+        <v>2473</v>
+      </c>
+      <c r="F1277" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1277" s="3" t="s">
+        <v>2474</v>
+      </c>
+      <c r="H1277" s="3">
+        <v>126</v>
+      </c>
+      <c r="I1277" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1277" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1278" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1278" s="3">
+        <v>1</v>
+      </c>
+      <c r="C1278" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1278" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E1278" s="3" t="s">
+        <v>2475</v>
+      </c>
+      <c r="F1278" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1278" s="3" t="s">
+        <v>2476</v>
+      </c>
+      <c r="H1278" s="3">
+        <v>69</v>
+      </c>
+      <c r="I1278" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1278" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
